--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_158_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_158_R16.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7384</v>
+        <v>3.3301</v>
       </c>
       <c r="E2" t="n">
-        <v>1.574</v>
+        <v>0.5617</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1644</v>
+        <v>2.7685</v>
       </c>
       <c r="G2" t="n">
-        <v>0.831</v>
+        <v>1.8588</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7708</v>
+        <v>-0.1119</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0602</v>
+        <v>1.9708</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1711</v>
+        <v>2.5595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6889999999999999</v>
+        <v>-0.1506</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4821</v>
+        <v>2.7101</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3401</v>
+        <v>-0.7007</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0818</v>
+        <v>0.0387</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.422</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0876</v>
+        <v>-0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1801</v>
+        <v>0.6311</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7389</v>
+        <v>-0.2867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5588</v>
+        <v>0.9177</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4544</v>
+        <v>3.1938</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6835</v>
+        <v>2.1638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7709</v>
+        <v>1.03</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9199</v>
+        <v>0.831</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2341</v>
+        <v>0.7708</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6859</v>
+        <v>0.0602</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9347</v>
+        <v>2.1711</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6672</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2676</v>
+        <v>1.4821</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0148</v>
+        <v>-1.3401</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4331</v>
+        <v>0.0818</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4183</v>
+        <v>-1.422</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.751</v>
+        <v>0.2752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9085</v>
+        <v>-0.1491</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8426</v>
+        <v>0.4244</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4373</v>
+        <v>2.3811</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.264</v>
+        <v>1.0844</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7013</v>
+        <v>1.2967</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8588</v>
+        <v>3.1748</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1119</v>
+        <v>2.3216</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9708</v>
+        <v>0.8532</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5595</v>
+        <v>4.4008</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1506</v>
+        <v>2.4402</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7101</v>
+        <v>1.9606</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7007</v>
+        <v>-1.226</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0387</v>
+        <v>-0.1186</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.1074</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7834</v>
+        <v>-3.4793</v>
       </c>
       <c r="R4" t="n">
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2618</v>
+        <v>-0.402</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1123</v>
+        <v>-0.3732</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8505</v>
+        <v>-0.0288</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6906</v>
+        <v>1.4778</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4947</v>
+        <v>0.9757</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1959</v>
+        <v>0.5021</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1748</v>
+        <v>1.9199</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3216</v>
+        <v>1.2341</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8532</v>
+        <v>0.6859</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4008</v>
+        <v>1.9347</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4402</v>
+        <v>1.6672</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9606</v>
+        <v>0.2676</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.226</v>
+        <v>-0.0148</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1186</v>
+        <v>-0.4331</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1074</v>
+        <v>0.4183</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0925</v>
+        <v>0.7745</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.963</v>
+        <v>0.2008</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1296</v>
+        <v>0.5737</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5361</v>
+        <v>-2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3617</v>
+        <v>1.3183</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3474</v>
+        <v>0.7752</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7091</v>
+        <v>0.5432</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4572</v>
+        <v>2.6508</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6579</v>
+        <v>1.5533</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2007</v>
+        <v>1.0975</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6393</v>
+        <v>3.3263</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0504</v>
+        <v>1.5965</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5889</v>
+        <v>1.7298</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1821</v>
+        <v>-0.6755</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6075</v>
+        <v>-0.0431</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7896</v>
+        <v>-0.6323</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4406</v>
+        <v>-0.3145</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5228</v>
+        <v>-0.3734</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9634</v>
+        <v>0.0589</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3183</v>
+        <v>1.2444</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7752</v>
+        <v>-0.2294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5432</v>
+        <v>1.4738</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6508</v>
+        <v>0.4572</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5533</v>
+        <v>0.6579</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0975</v>
+        <v>-0.2007</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3263</v>
+        <v>0.6393</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5965</v>
+        <v>0.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7298</v>
+        <v>0.5889</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6755</v>
+        <v>-0.1821</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0431</v>
+        <v>0.6075</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6323</v>
+        <v>-0.7896</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3145</v>
+        <v>0.3233</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>-0.4048</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0589</v>
+        <v>0.7281</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2405</v>
+        <v>0.5437</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.669</v>
+        <v>-0.4331</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9096</v>
+        <v>0.9768</v>
       </c>
       <c r="G8" t="n">
         <v>0.3739</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4349</v>
+        <v>-0.1318</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9709</v>
+        <v>-0.735</v>
       </c>
       <c r="U8" t="n">
-        <v>0.536</v>
+        <v>0.6032</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5755</v>
+        <v>-1.1145</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8041</v>
+        <v>-2.2759</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2286</v>
+        <v>1.1614</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8244</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3365</v>
+        <v>-0.2025</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>-0.2082</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0732</v>
+        <v>-1.6117</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6089</v>
+        <v>-2.3499</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5357</v>
+        <v>0.7382</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3516</v>
+        <v>-1.1164</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8777</v>
+        <v>-0.6446</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.2293</v>
+        <v>-0.4718</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9867</v>
+        <v>-1.5559</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1883</v>
+        <v>-0.7695</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.175</v>
+        <v>-0.7863</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.365</v>
+        <v>0.4395</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6893</v>
+        <v>0.1249</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0543</v>
+        <v>0.3145</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0876</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.727</v>
+        <v>-0.2634</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6097</v>
+        <v>-0.3301</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1173</v>
+        <v>0.0668</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8641</v>
+        <v>-1.6636</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4679</v>
+        <v>-2.4345</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6038</v>
+        <v>0.771</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1164</v>
+        <v>-3.3516</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6446</v>
+        <v>0.8777</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4718</v>
+        <v>-4.2293</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5559</v>
+        <v>-1.9867</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7695</v>
+        <v>0.1883</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7863</v>
+        <v>-2.175</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4395</v>
+        <v>-1.365</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1249</v>
+        <v>0.6893</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>-2.0543</v>
       </c>
       <c r="P11" t="n">
+        <v>2.0876</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.4639</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5157</v>
+        <v>0.1366</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4481</v>
+        <v>-0.2159</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0677</v>
+        <v>0.3525</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.1479</v>
+        <v>-9.5189</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.3056</v>
+        <v>-8.7774</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8423</v>
+        <v>-0.7415</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7208</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7042</v>
+        <v>0.3332</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3031</v>
+        <v>-0.1687</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4011</v>
+        <v>0.5019</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5799</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4194999999999993</v>
+        <v>-0.4195000000000029</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.9395</v>
+        <v>-10.9394</v>
       </c>
       <c r="F13" t="n">
         <v>10.5202</v>
@@ -1435,16 +1435,16 @@
         <v>2.2532</v>
       </c>
       <c r="H13" t="n">
-        <v>6.452500000000001</v>
+        <v>6.4525</v>
       </c>
       <c r="I13" t="n">
         <v>-4.1991</v>
       </c>
       <c r="J13" t="n">
-        <v>8.990400000000001</v>
+        <v>8.990399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2235</v>
+        <v>4.223500000000001</v>
       </c>
       <c r="L13" t="n">
         <v>4.766999999999998</v>
@@ -1468,13 +1468,13 @@
         <v>18.5564</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1598</v>
+        <v>1.1597</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0445</v>
+        <v>-3.0443</v>
       </c>
       <c r="U13" t="n">
-        <v>4.2042</v>
+        <v>4.2041</v>
       </c>
       <c r="V13" t="n">
         <v>-3.8324</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4643</v>
+        <v>3.9081</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7561</v>
+        <v>1.1664</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7081</v>
+        <v>2.7417</v>
       </c>
       <c r="G14" t="n">
         <v>0.0805</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3631</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7512</v>
+        <v>0.1614</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6119</v>
+        <v>0.6456</v>
       </c>
       <c r="V14" t="n">
         <v>1.8608</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7569</v>
+        <v>2.4367</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9053</v>
+        <v>1.4951</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8516</v>
+        <v>0.9416</v>
       </c>
       <c r="G15" t="n">
         <v>3.0444</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9137</v>
+        <v>-0.2339</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8883</v>
+        <v>-0.2985</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0255</v>
+        <v>0.0646</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3179</v>
+        <v>1.3743</v>
       </c>
       <c r="E16" t="n">
         <v>1.0216</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2963</v>
+        <v>0.3527</v>
       </c>
       <c r="G16" t="n">
         <v>3.2328</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0593</v>
+        <v>-0.0029</v>
       </c>
       <c r="T16" t="n">
         <v>-0.326</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2667</v>
+        <v>0.3231</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2679</v>
+        <v>0.7796</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3449</v>
+        <v>-0.6988</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6128</v>
+        <v>1.4784</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1835</v>
@@ -1780,13 +1780,13 @@
         <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7556</v>
+        <v>0.2673</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0395</v>
+        <v>-0.3143</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7161</v>
+        <v>0.5816</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3593</v>
+        <v>0.2756</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9025</v>
+        <v>-0.7846</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2618</v>
+        <v>1.0601</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5597</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2407</v>
+        <v>-0.3244</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3567</v>
+        <v>0.1551</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1911</v>
+        <v>0.1632</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1636</v>
+        <v>-0.2816</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3547</v>
+        <v>0.4448</v>
       </c>
       <c r="G19" t="n">
         <v>0.8829</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0378</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2513</v>
+        <v>-0.3692</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2891</v>
+        <v>0.3791</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9615</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.412</v>
+        <v>-0.3949</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.202</v>
+        <v>-2.0841</v>
       </c>
       <c r="F20" t="n">
-        <v>1.79</v>
+        <v>1.6892</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0352</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0004</v>
+        <v>0.0167</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8962</v>
+        <v>-0.7782</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5517</v>
+        <v>-1.4001</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9255</v>
+        <v>-1.8076</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3739</v>
+        <v>0.4075</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5637</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0602</v>
+        <v>0.0914</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1023</v>
+        <v>-1.6426</v>
       </c>
       <c r="E23" t="n">
         <v>-3.391</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2887</v>
+        <v>1.7484</v>
       </c>
       <c r="G23" t="n">
         <v>-1.405</v>
@@ -2248,13 +2248,13 @@
         <v>3.2473</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8597</v>
+        <v>-0.4</v>
       </c>
       <c r="T23" t="n">
         <v>-0.55</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3097</v>
+        <v>0.15</v>
       </c>
       <c r="V23" t="n">
         <v>0.3943</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2931</v>
+        <v>-3.7154</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7351</v>
+        <v>-5.6171</v>
       </c>
       <c r="F24" t="n">
-        <v>1.442</v>
+        <v>1.9017</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2425</v>
@@ -2326,13 +2326,13 @@
         <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1075</v>
+        <v>-0.5298</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1123</v>
+        <v>-0.9944</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0048</v>
+        <v>0.4646</v>
       </c>
       <c r="V24" t="n">
         <v>1.6083</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4194999999999984</v>
+        <v>1.205699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.0563</v>
+        <v>-11.0564</v>
       </c>
       <c r="F25" t="n">
-        <v>11.4758</v>
+        <v>12.262</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2531</v>
@@ -2404,13 +2404,13 @@
         <v>18.5563</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1597</v>
+        <v>-0.3734000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.204300000000001</v>
+        <v>-4.2042</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0443</v>
+        <v>3.8307</v>
       </c>
       <c r="V25" t="n">
         <v>3.8323</v>
